--- a/przyklad_import_odbiorcy.xlsx
+++ b/przyklad_import_odbiorcy.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Odbiorcy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Recipients" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,31 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E74B5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF0FB"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -57,31 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,76 +413,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Imię i Nazwisko / Nazwa</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email (opcjonalnie)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Telefon (opcjonalnie)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Jan Kowalski</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>jan.kowalski@brueggen.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>+48 600 100 200</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Anna Nowak</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>a.nowak@brueggen.com</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Piotr Wiśniewski</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>+48 600 300 400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Maria Wójcik</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>m.wojcik@brueggen.com</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Tomasz Zieliński</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
